--- a/PCB/Dock Rev6/Productions Files/BOM.xlsx
+++ b/PCB/Dock Rev6/Productions Files/BOM.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="33">
   <si>
     <t xml:space="preserve">﻿Designator</t>
   </si>
@@ -63,36 +63,6 @@
     <t xml:space="preserve">C15850</t>
   </si>
   <si>
-    <t xml:space="preserve">C6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100uF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CP_Radial_D5.0mm_P2.50mm</t>
-  </si>
-  <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
-    <t xml:space="preserve">D1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MHL512IR059CRT 940nm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IR_LED_THT_D1_with_Assembly3D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C405273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D2,D3,D4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LED_5mm_Green_THT</t>
-  </si>
-  <si>
     <t xml:space="preserve">D5</t>
   </si>
   <si>
@@ -105,18 +75,6 @@
     <t xml:space="preserve">C965807</t>
   </si>
   <si>
-    <t xml:space="preserve">J1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HX-XH2.54-2PZZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HX-XH2.54-2PZZ_C42391660</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C42391660</t>
-  </si>
-  <si>
     <t xml:space="preserve">Q1</t>
   </si>
   <si>
@@ -166,36 +124,6 @@
   </si>
   <si>
     <t xml:space="preserve">C25803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R5,R6,R7,R8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39R 0.5W</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R_Axial_DIN0411_L9.9mm_D3.6mm_P15.24mm_Horizontal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SW1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KH-6X6X5H-ZJ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SW-TH_KH-6X6X5H-ZJ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C2837541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CC1101 433MHz COIL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CC1101_433MHz_Coil_Module_2x04_P2.54mm</t>
   </si>
 </sst>
 </file>
@@ -558,7 +486,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
@@ -642,38 +570,38 @@
         <v>20</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D6" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" t="s">
         <v>22</v>
       </c>
-      <c r="B7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" t="s">
-        <v>24</v>
-      </c>
       <c r="D7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D8" t="s">
         <v>29</v>
@@ -687,108 +615,10 @@
         <v>31</v>
       </c>
       <c r="C9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" t="s">
         <v>32</v>
-      </c>
-      <c r="D9" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" t="s">
-        <v>34</v>
-      </c>
-      <c r="B10" t="s">
-        <v>35</v>
-      </c>
-      <c r="C10" t="s">
-        <v>36</v>
-      </c>
-      <c r="D10" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" t="s">
-        <v>38</v>
-      </c>
-      <c r="B11" t="s">
-        <v>39</v>
-      </c>
-      <c r="C11" t="s">
-        <v>36</v>
-      </c>
-      <c r="D11" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" t="s">
-        <v>41</v>
-      </c>
-      <c r="B12" t="s">
-        <v>42</v>
-      </c>
-      <c r="C12" t="s">
-        <v>36</v>
-      </c>
-      <c r="D12" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" t="s">
-        <v>44</v>
-      </c>
-      <c r="B13" t="s">
-        <v>45</v>
-      </c>
-      <c r="C13" t="s">
-        <v>36</v>
-      </c>
-      <c r="D13" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" t="s">
-        <v>47</v>
-      </c>
-      <c r="B14" t="s">
-        <v>48</v>
-      </c>
-      <c r="C14" t="s">
-        <v>49</v>
-      </c>
-      <c r="D14" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" t="s">
-        <v>50</v>
-      </c>
-      <c r="B15" t="s">
-        <v>51</v>
-      </c>
-      <c r="C15" t="s">
-        <v>52</v>
-      </c>
-      <c r="D15" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" t="s">
-        <v>54</v>
-      </c>
-      <c r="B16" t="s">
-        <v>55</v>
-      </c>
-      <c r="C16" t="s">
-        <v>56</v>
-      </c>
-      <c r="D16" t="s">
-        <v>15</v>
       </c>
     </row>
   </sheetData>
